--- a/Excel/Excel Workbook/Functions/AVERAGE Example.xlsx
+++ b/Excel/Excel Workbook/Functions/AVERAGE Example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\My Projects\Data Projects\My Data Science Full Kit\Complete_Data_Science_Full_Course\Excel\Excel Workbook\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\My Projects\Data Projects\My Data Science Full Kit\Complete_Data_Science_Full_Course\Excel\Excel Workbook\Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7418EF-DBA3-46E9-82A6-7ADA6F397942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDEA5AED-26CE-40E4-8F68-D25D30120655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="15600" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -390,12 +390,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="8.7265625" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -415,7 +418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -432,7 +435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -449,7 +452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -466,7 +469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -483,7 +486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -500,7 +503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -517,7 +520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
